--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Secret.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Secret.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="164">
   <si>
     <t>Property</t>
   </si>
@@ -480,6 +480,14 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>CX.7 + CX.8</t>
   </si>
   <si>
@@ -503,6 +511,10 @@
   </si>
   <si>
     <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -1530,7 +1542,7 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>83</v>
@@ -1805,7 +1817,9 @@
       <c r="M9" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N9" s="2"/>
+      <c r="N9" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -1863,27 +1877,27 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1906,16 +1920,16 @@
         <v>105</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -1965,7 +1979,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1974,19 +1988,19 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Secret.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Secret.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -480,14 +480,6 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>CX.7 + CX.8</t>
   </si>
   <si>
@@ -511,10 +503,6 @@
   </si>
   <si>
     <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -1542,7 +1530,7 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>83</v>
@@ -1817,9 +1805,7 @@
       <c r="M9" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N9" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -1877,27 +1863,27 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AK9" t="s" s="2">
+      <c r="AM9" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1920,16 +1906,16 @@
         <v>105</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -1979,7 +1965,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1988,19 +1974,19 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
